--- a/002/002_AreasTributarias_NOSE_DOCK_H5_H6_R1.3_3.xlsx
+++ b/002/002_AreasTributarias_NOSE_DOCK_H5_H6_R1.3_3.xlsx
@@ -1207,7 +1207,7 @@
     <t xml:space="preserve">Franja superior de muros laterales que va a las vigas de alero</t>
   </si>
   <si>
-    <t xml:space="preserve">C. MURO FRONTAL — EJE 1 (Z = 0) — LARGUEROS MC4-14, MC10-12 Y MC10-14; DINTEL MCC10-14 (R1.3_3: LARGUEROS A 0.60 M, @1.20 M Y A 9.45 M)</t>
+    <t xml:space="preserve">C. MURO FRONTAL — EJE 1 (Z = 0) — LARGUEROS MC4-14, MC10-12 Y MC10-14; DINTEL Y LARGUERO DE 9.45 M MCC10-14 (R1.3_3: LARGUEROS A 0.60 M, @1.20 M Y A 9.45 M)</t>
   </si>
   <si>
     <t xml:space="preserve">Vanos: puerta de 1.22 × 2.40 m (X 0.60 a 1.82) con jambas HSS2 hasta el larguero de 3.00 m y dintel a 2.40 m; vano del nose dock de 5.10 × 6.60 m (X 2.32 a 7.42), sin carga. El dintel de la cortina va en la línea de 6.60 m. La franja de la base (0.00–0.30 m) baja directo a la cimentación.</t>
@@ -2068,10 +2068,10 @@
     <t xml:space="preserve">Largueros muros A/B claro 1-2 (0.60 a 7.80 m) y larguero 7.80 m del muro 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Largueros muros A/B claro 2-3, 9.00 m claro 1-2 y 9.00/9.45 m del muro 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Largueros en cajón (9.45 m claro 1-2, 9.00 m claro 2-3) y dintel de 6.60 m</t>
+    <t xml:space="preserve">Largueros muros A/B claro 2-3, 9.00 m claro 1-2 y 9.00 m del muro 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remates de contraflambeos en cajón (9.45 m claro 1-2, 9.00 m claro 2-3 y 9.45 m del muro 1) y dintel de 6.60 m</t>
   </si>
   <si>
     <t xml:space="preserve">Largueros cortos del muro 1 y dintel de puerta</t>
@@ -12236,7 +12236,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="E95" s="23" t="n">
         <v>9.45</v>
@@ -16619,13 +16619,13 @@
         <v>462</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>124.16</v>
+        <v>114.08</v>
       </c>
       <c r="D32" s="33" t="n">
         <v>8.2789</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>805.198</v>
+        <v>739.831</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>680</v>
@@ -16636,13 +16636,13 @@
         <v>448</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>42.08</v>
+        <v>52.16</v>
       </c>
       <c r="D33" s="33" t="n">
         <v>16.5577</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>545.791</v>
+        <v>676.532</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>681</v>
@@ -16833,7 +16833,7 @@
       <c r="D41" s="8"/>
       <c r="E41" s="19" t="n">
         <f aca="false">SUM(E23:E40)</f>
-        <v>6880.449</v>
+        <v>6945.823</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>696</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C45" s="11" t="n">
         <f aca="false">E41/1000</f>
-        <v>6.880449</v>
+        <v>6.945823</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>699</v>
@@ -16964,7 +16964,7 @@
       </c>
       <c r="C50" s="11" t="n">
         <f aca="false">SUM(C45:C49)</f>
-        <v>12.607225878</v>
+        <v>12.672599878</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>699</v>

--- a/002/002_AreasTributarias_NOSE_DOCK_H5_H6_R1.3_3.xlsx
+++ b/002/002_AreasTributarias_NOSE_DOCK_H5_H6_R1.3_3.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="752">
   <si>
     <t xml:space="preserve">ÁREAS TRIBUTARIAS Y CARGAS PARA STAAD — HANGAR NOSE-DOCK H5-H6 — DATOS</t>
   </si>
@@ -292,7 +292,7 @@
     <t xml:space="preserve">1. Los contraflambeos PIPS7 del techo no se consideran portantes (articulados en sus extremos): cada larguero MC12-14 trabaja de alero a alero (10.08 m) y entrega la mitad a cada viga de alero MCE12-14.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. En los ejes 1, 2 y 3 no hay larguero en el modelo: la franja de ese eje la toma directo la viga del marco (VM-1 MCE4-14, VM-2 MCE10-14, VM-3 MCE6-14).</t>
+    <t xml:space="preserve">2. En los ejes 1, 2 y 3 no hay larguero en el modelo: la franja de ese eje la toma directo la viga del marco (VM-1, VM-2 y VM-3 MCE10-14).</t>
   </si>
   <si>
     <t xml:space="preserve">3. Techo: franja de cada línea = mitad de la separación a cada lado. Muros: igual en vertical; la franja de abajo (0.00–0.30 m) baja directo a la base y la de arriba va a la viga de alero (ejes A y B) o a la VM-1 (eje 1). Los vanos no llevan lámina: la cortina carga su peso arriba de las jambas (nodos 69 y 70) y su viento a las jambas; la puerta de 1.22 × 2.40 carga su viento a su dintel (hoja de viento).</t>
@@ -361,7 +361,7 @@
     <t xml:space="preserve">7. El peso propio del acero lo calcula STAAD (SELFWEIGHT Y −1 en el caso 1; SELFWEIGHT X 1 y Z 1 en la masa del caso 4). La CM y la CV de techo van en largueros y vigas; la masa sísmica del techo y de los muros va puntual en las cabezas de columna.</t>
   </si>
   <si>
-    <t xml:space="preserve">TECHO — ÁREAS TRIBUTARIAS DE LARGUEROS MC12-14 Y VIGAS DE MARCO MCE4-14, MCE10-14 Y MCE6-14 (R1.3_3)</t>
+    <t xml:space="preserve">TECHO — ÁREAS TRIBUTARIAS DE LARGUEROS MC12-14 Y VIGAS DE MARCO MCE10-14 (R1.3_3)</t>
   </si>
   <si>
     <t xml:space="preserve">Planta en proyección horizontal. Las líneas en X (largueros LT y vigas de marco VM) reciben su franja; las vigas de alero VA y VB reciben la mitad del claro de cada larguero. Mismas áreas que el DXF R1.3_3. En STAAD la CM y la CV van en UNI GY en cada línea con su franja b (hoja STAAD); la masa del techo va a las cabezas de columna (hoja NODOS_TECHO).</t>
@@ -457,7 +457,7 @@
     <t xml:space="preserve">Viga de marco eje 1</t>
   </si>
   <si>
-    <t xml:space="preserve">MCE4-14</t>
+    <t xml:space="preserve">MCE10-14</t>
   </si>
   <si>
     <t xml:space="preserve">11 48 TO 51</t>
@@ -532,9 +532,6 @@
     <t xml:space="preserve">Viga de marco eje 2</t>
   </si>
   <si>
-    <t xml:space="preserve">MCE10-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">74 121 TO 124</t>
   </si>
   <si>
@@ -574,9 +571,6 @@
     <t xml:space="preserve">Viga de marco eje 3</t>
   </si>
   <si>
-    <t xml:space="preserve">MCE6-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">12 52 TO 55</t>
   </si>
   <si>
@@ -2059,6 +2053,9 @@
     <t xml:space="preserve">Columnas eje 3</t>
   </si>
   <si>
+    <t xml:space="preserve">Vigas de marco (ejes 1, 2 y 3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vigas de alero</t>
   </si>
   <si>
@@ -2170,10 +2167,10 @@
     <t xml:space="preserve">W dinámico de STAAD — dirección X</t>
   </si>
   <si>
-    <t xml:space="preserve">DYNAMIC WEIGHT del análisis modal R1.3_3 (43 modos); igual en X y en Z.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hoja de sismo 002_SISMO_VIENTO_SALVADOR_R1.3_3.xlsx</t>
+    <t xml:space="preserve">DYNAMIC WEIGHT de la corrida R1.3_3 (43 modos); igual en X y en Z.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.ANL R1.3_3</t>
   </si>
   <si>
     <t xml:space="preserve">5. CORTANTE MÍNIMO NTDS §5.4.1(3) → FACTOR DEL SPECTRUM EN STAAD</t>
@@ -2233,16 +2230,16 @@
     <t xml:space="preserve">T_B en X (modo con más masa en X)</t>
   </si>
   <si>
-    <t xml:space="preserve">Modo 1: mayor participación en X (82.30%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hoja de sismo R1.3_3 (43 modos)</t>
+    <t xml:space="preserve">Modo 1: mayor participación en X (83.21%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.ANL R1.3_3 (43 modos)</t>
   </si>
   <si>
     <t xml:space="preserve">T_B en Z (modo con más masa en Z)</t>
   </si>
   <si>
-    <t xml:space="preserve">Modo 5: mayor participación en Z (85.09%).</t>
+    <t xml:space="preserve">Modo 5: mayor participación en Z (89.42%).</t>
   </si>
   <si>
     <t xml:space="preserve">V_est en X = máx(Cs(T_B), 0.8·Cs(T_A))·W</t>
@@ -2266,22 +2263,25 @@
     <t xml:space="preserve">V modal en X (sin factor)</t>
   </si>
   <si>
-    <t xml:space="preserve">SRSS de STAAD sin el factor de dirección.</t>
+    <t xml:space="preserve">SRSS de STAAD (1777.54 kg) entre el factor usado (1.0962).</t>
   </si>
   <si>
     <t xml:space="preserve">V modal en Z (sin factor)</t>
   </si>
   <si>
+    <t xml:space="preserve">SRSS de STAAD (2067.14 kg) entre el factor usado (1.0550).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Factor del SPECTRUM en X</t>
   </si>
   <si>
-    <t xml:space="preserve">Factor final para SPECTRUM X.</t>
+    <t xml:space="preserve">Factor mínimo requerido en X; el .STD usa 1.0962, que lo cubre.</t>
   </si>
   <si>
     <t xml:space="preserve">Factor del SPECTRUM en Z</t>
   </si>
   <si>
-    <t xml:space="preserve">Factor final para SPECTRUM Z.</t>
+    <t xml:space="preserve">Factor mínimo requerido en Z; el .STD usa 1.0550, que lo cubre.</t>
   </si>
 </sst>
 </file>
@@ -4286,7 +4286,7 @@
         <v>167</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>10</v>
@@ -4332,15 +4332,15 @@
         <v>151.2</v>
       </c>
       <c r="P14" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q14" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="Q14" s="10" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>147</v>
@@ -4392,15 +4392,15 @@
         <v>151.2</v>
       </c>
       <c r="P15" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q15" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>147</v>
@@ -4452,15 +4452,15 @@
         <v>151.2</v>
       </c>
       <c r="P16" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q16" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="Q16" s="10" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>147</v>
@@ -4512,21 +4512,21 @@
         <v>151.2</v>
       </c>
       <c r="P17" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q17" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="Q17" s="10" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>181</v>
-      </c>
       <c r="D18" s="8" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>16</v>
@@ -4572,18 +4572,18 @@
         <v>75.6</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25"/>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="21" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -4623,7 +4623,7 @@
     </row>
     <row r="22" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -4646,13 +4646,13 @@
         <v>114</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>116</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>118</v>
@@ -4661,28 +4661,28 @@
         <v>119</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>122</v>
       </c>
       <c r="K23" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="M23" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="L23" s="5" t="s">
+      <c r="N23" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="M23" s="5" t="s">
+      <c r="O23" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>197</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>128</v>
@@ -4697,32 +4697,32 @@
       <c r="D24" s="20"/>
       <c r="E24" s="20"/>
       <c r="F24" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H24" s="20" t="s">
         <v>132</v>
       </c>
       <c r="I24" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="K24" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="L24" s="20" t="s">
         <v>201</v>
-      </c>
-      <c r="K24" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="L24" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="M24" s="20"/>
       <c r="N24" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P24" s="20" t="s">
         <v>140</v>
@@ -4731,16 +4731,16 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="E25" s="8" t="s">
         <v>207</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>209</v>
       </c>
       <c r="F25" s="22" t="n">
         <f aca="false">F8</f>
@@ -4782,24 +4782,24 @@
         <v>147</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q25" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>212</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>214</v>
       </c>
       <c r="F26" s="22" t="n">
         <f aca="false">F15</f>
@@ -4841,24 +4841,24 @@
         <v>151.2</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q26" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F27" s="22" t="n">
         <f aca="false">F8</f>
@@ -4900,24 +4900,24 @@
         <v>147</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q27" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F28" s="22" t="n">
         <f aca="false">F15</f>
@@ -4959,18 +4959,18 @@
         <v>151.2</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Q28" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="25"/>
@@ -5035,7 +5035,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -5057,7 +5057,7 @@
     </row>
     <row r="2" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -5080,7 +5080,7 @@
     <row r="3" s="1" customFormat="true" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -5105,40 +5105,40 @@
         <v>114</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>118</v>
       </c>
       <c r="L5" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>239</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>122</v>
@@ -5147,10 +5147,10 @@
         <v>123</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="S5" s="5" t="s">
         <v>7</v>
@@ -5168,34 +5168,34 @@
         <v>129</v>
       </c>
       <c r="H6" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="K6" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="L6" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="M6" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="N6" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="O6" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="M6" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="N6" s="20" t="s">
+      <c r="P6" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="O6" s="20" t="s">
+      <c r="Q6" s="20" t="s">
         <v>247</v>
-      </c>
-      <c r="P6" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q6" s="20" t="s">
-        <v>249</v>
       </c>
       <c r="R6" s="20" t="s">
         <v>140</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>1</v>
@@ -5216,7 +5216,7 @@
         <v>0.6</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G7" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -5260,18 +5260,18 @@
         <v>-0.05265</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>1</v>
@@ -5280,7 +5280,7 @@
         <v>0.6</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G8" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -5324,18 +5324,18 @@
         <v>-0.05265</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>2</v>
@@ -5344,7 +5344,7 @@
         <v>1.8</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G9" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -5388,18 +5388,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
@@ -5408,7 +5408,7 @@
         <v>1.8</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G10" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -5452,18 +5452,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>3</v>
@@ -5472,7 +5472,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G11" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -5516,18 +5516,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>3</v>
@@ -5536,7 +5536,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G12" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -5580,18 +5580,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="21" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>4</v>
@@ -5600,7 +5600,7 @@
         <v>4.2</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G13" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -5644,18 +5644,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>4</v>
@@ -5664,7 +5664,7 @@
         <v>4.2</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G14" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -5708,18 +5708,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>5</v>
@@ -5728,7 +5728,7 @@
         <v>5.4</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G15" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -5772,18 +5772,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>5</v>
@@ -5792,7 +5792,7 @@
         <v>5.4</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G16" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -5836,18 +5836,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>6</v>
@@ -5856,7 +5856,7 @@
         <v>6.6</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G17" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -5900,18 +5900,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
@@ -5920,7 +5920,7 @@
         <v>6.6</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G18" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -5964,18 +5964,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>7</v>
@@ -5984,7 +5984,7 @@
         <v>7.8</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G19" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -6028,18 +6028,18 @@
         <v>-0.0702000000000001</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>7</v>
@@ -6048,7 +6048,7 @@
         <v>7.8</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G20" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -6092,18 +6092,18 @@
         <v>-0.0702000000000001</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>8</v>
@@ -6112,7 +6112,7 @@
         <v>9</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G21" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -6156,18 +6156,18 @@
         <v>-0.0482625</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="21" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>8</v>
@@ -6176,7 +6176,7 @@
         <v>9</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G22" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -6222,18 +6222,18 @@
         <v>-0.05720247</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="21" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>9</v>
@@ -6242,7 +6242,7 @@
         <v>9.45</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G23" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -6288,18 +6288,18 @@
         <v>-0.0342409275</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="S23" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>1</v>
@@ -6308,7 +6308,7 @@
         <v>0.6</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G24" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -6352,18 +6352,18 @@
         <v>-0.05265</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="S24" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>1</v>
@@ -6372,7 +6372,7 @@
         <v>0.6</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G25" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -6416,18 +6416,18 @@
         <v>-0.05265</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="S25" s="10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>2</v>
@@ -6436,7 +6436,7 @@
         <v>1.8</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G26" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -6480,18 +6480,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="S26" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>2</v>
@@ -6500,7 +6500,7 @@
         <v>1.8</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G27" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -6544,18 +6544,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R27" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>3</v>
@@ -6564,7 +6564,7 @@
         <v>3</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G28" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -6608,18 +6608,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R28" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>3</v>
@@ -6628,7 +6628,7 @@
         <v>3</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G29" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -6672,18 +6672,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>4</v>
@@ -6692,7 +6692,7 @@
         <v>4.2</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G30" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -6736,18 +6736,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R30" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="S30" s="10" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>4</v>
@@ -6756,7 +6756,7 @@
         <v>4.2</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G31" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -6800,18 +6800,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="S31" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="21" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>5</v>
@@ -6820,7 +6820,7 @@
         <v>5.4</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G32" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -6864,18 +6864,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S32" s="10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>5</v>
@@ -6884,7 +6884,7 @@
         <v>5.4</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G33" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -6928,18 +6928,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R33" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S33" s="10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
@@ -6948,7 +6948,7 @@
         <v>6.6</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G34" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -6992,18 +6992,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R34" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="S34" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="21" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>6</v>
@@ -7012,7 +7012,7 @@
         <v>6.6</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G35" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -7056,18 +7056,18 @@
         <v>-0.0702</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="S35" s="10" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="21" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>7</v>
@@ -7076,7 +7076,7 @@
         <v>7.8</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G36" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -7120,18 +7120,18 @@
         <v>-0.0702000000000001</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="21" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>7</v>
@@ -7140,7 +7140,7 @@
         <v>7.8</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G37" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -7184,18 +7184,18 @@
         <v>-0.0702000000000001</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="S37" s="10" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="21" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>8</v>
@@ -7204,7 +7204,7 @@
         <v>9</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G38" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -7248,18 +7248,18 @@
         <v>-0.0482625</v>
       </c>
       <c r="R38" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="21" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>8</v>
@@ -7268,7 +7268,7 @@
         <v>9</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G39" s="23" t="n">
         <f aca="false">DATOS!$C$33-DATOS!$C$32</f>
@@ -7314,18 +7314,18 @@
         <v>-0.05720247</v>
       </c>
       <c r="R39" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S39" s="10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>9</v>
@@ -7334,7 +7334,7 @@
         <v>9.45</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G40" s="23" t="n">
         <f aca="false">DATOS!$C$32-DATOS!$C$31</f>
@@ -7380,18 +7380,18 @@
         <v>-0.0342409275</v>
       </c>
       <c r="R40" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="S40" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D41" s="25"/>
       <c r="E41" s="25"/>
@@ -7411,7 +7411,7 @@
     </row>
     <row r="43" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -7433,7 +7433,7 @@
     </row>
     <row r="44" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -7455,41 +7455,41 @@
     </row>
     <row r="45" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F45" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="I45" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="J45" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="H45" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="I45" s="5" t="s">
+      <c r="K45" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="J45" s="5" t="s">
+      <c r="L45" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="K45" s="5" t="s">
+      <c r="M45" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="L45" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="M45" s="5" t="s">
-        <v>366</v>
-      </c>
       <c r="N45" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O45" s="5" t="s">
         <v>122</v>
@@ -7498,7 +7498,7 @@
         <v>123</v>
       </c>
       <c r="Q45" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="R45" s="5"/>
       <c r="S45" s="5" t="s">
@@ -7519,7 +7519,7 @@
         <v>129</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I46" s="20" t="s">
         <v>129</v>
@@ -7528,25 +7528,25 @@
         <v>129</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="L46" s="20" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="M46" s="20" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="N46" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="O46" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="P46" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="O46" s="20" t="s">
+      <c r="Q46" s="20" t="s">
         <v>247</v>
-      </c>
-      <c r="P46" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q46" s="20" t="s">
-        <v>249</v>
       </c>
       <c r="R46" s="20"/>
       <c r="S46" s="20"/>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="47" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="27" t="n">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="R47" s="8"/>
       <c r="S47" s="10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="T47" s="0"/>
       <c r="U47" s="0"/>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="48" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="27" t="n">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="R48" s="8"/>
       <c r="S48" s="10" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="T48" s="0"/>
       <c r="U48" s="0"/>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="49" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="27" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="R49" s="8"/>
       <c r="S49" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="T49" s="0"/>
       <c r="U49" s="0"/>
@@ -7907,10 +7907,10 @@
     </row>
     <row r="50" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="27" t="n">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="R50" s="8"/>
       <c r="S50" s="10" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T50" s="0"/>
       <c r="U50" s="0"/>
@@ -8011,10 +8011,10 @@
     </row>
     <row r="51" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="27" t="n">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="R51" s="8"/>
       <c r="S51" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="T51" s="0"/>
       <c r="U51" s="0"/>
@@ -8115,10 +8115,10 @@
     </row>
     <row r="52" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="27" t="n">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="R52" s="8"/>
       <c r="S52" s="10" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T52" s="0"/>
       <c r="U52" s="0"/>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="53" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="27" t="n">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="R53" s="8"/>
       <c r="S53" s="10" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="T53" s="0"/>
       <c r="U53" s="0"/>
@@ -8323,10 +8323,10 @@
     </row>
     <row r="54" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="27" t="n">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="R54" s="8"/>
       <c r="S54" s="10" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="T54" s="0"/>
       <c r="U54" s="0"/>
@@ -8426,10 +8426,10 @@
     </row>
     <row r="55" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="27" t="n">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="R55" s="8"/>
       <c r="S55" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="T55" s="0"/>
       <c r="U55" s="0"/>
@@ -8529,10 +8529,10 @@
     </row>
     <row r="56" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="27" t="n">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="R56" s="8"/>
       <c r="S56" s="10" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="T56" s="0"/>
       <c r="U56" s="0"/>
@@ -8632,10 +8632,10 @@
     </row>
     <row r="57" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="27" t="n">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="R57" s="8"/>
       <c r="S57" s="10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="T57" s="0"/>
       <c r="U57" s="0"/>
@@ -8735,10 +8735,10 @@
     </row>
     <row r="58" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="27" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="R58" s="8"/>
       <c r="S58" s="10" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="T58" s="0"/>
       <c r="U58" s="0"/>
@@ -8839,10 +8839,10 @@
     </row>
     <row r="59" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="27" t="n">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="R59" s="8"/>
       <c r="S59" s="10" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="T59" s="0"/>
       <c r="U59" s="0"/>
@@ -8943,10 +8943,10 @@
     </row>
     <row r="60" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="27" t="n">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="R60" s="8"/>
       <c r="S60" s="10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="T60" s="0"/>
       <c r="U60" s="0"/>
@@ -9047,10 +9047,10 @@
     </row>
     <row r="61" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D61" s="8"/>
       <c r="E61" s="27" t="n">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="R61" s="8"/>
       <c r="S61" s="10" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="T61" s="0"/>
       <c r="U61" s="0"/>
@@ -9151,10 +9151,10 @@
     </row>
     <row r="62" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="27" t="n">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="R62" s="8"/>
       <c r="S62" s="10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="T62" s="0"/>
       <c r="U62" s="0"/>
@@ -9255,10 +9255,10 @@
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="27" t="n">
@@ -9312,15 +9312,15 @@
       </c>
       <c r="R63" s="8"/>
       <c r="S63" s="10" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="27" t="n">
@@ -9374,15 +9374,15 @@
       </c>
       <c r="R64" s="8"/>
       <c r="S64" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="27" t="n">
@@ -9435,15 +9435,15 @@
       </c>
       <c r="R65" s="8"/>
       <c r="S65" s="10" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="27" t="n">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="R66" s="8"/>
       <c r="S66" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="T66" s="0"/>
       <c r="U66" s="0"/>
@@ -9543,10 +9543,10 @@
     </row>
     <row r="67" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="27" t="n">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="R67" s="8"/>
       <c r="S67" s="10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="T67" s="0"/>
       <c r="U67" s="0"/>
@@ -9646,10 +9646,10 @@
     </row>
     <row r="68" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="27" t="n">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="R68" s="8"/>
       <c r="S68" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="T68" s="0"/>
       <c r="U68" s="0"/>
@@ -9749,10 +9749,10 @@
     </row>
     <row r="69" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D69" s="25"/>
       <c r="E69" s="25"/>
@@ -9858,7 +9858,7 @@
     </row>
     <row r="71" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -9922,7 +9922,7 @@
     </row>
     <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
@@ -9989,28 +9989,28 @@
         <v>114</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>116</v>
       </c>
       <c r="E73" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="G73" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="H73" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J73" s="5" t="s">
         <v>396</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="I73" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="J73" s="5" t="s">
-        <v>398</v>
       </c>
       <c r="K73" s="5" t="s">
         <v>118</v>
@@ -10019,7 +10019,7 @@
         <v>119</v>
       </c>
       <c r="M73" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N73" s="5" t="s">
         <v>122</v>
@@ -10028,10 +10028,10 @@
         <v>123</v>
       </c>
       <c r="P73" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q73" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="R73" s="5"/>
       <c r="S73" s="5" t="s">
@@ -10097,28 +10097,28 @@
         <v>132</v>
       </c>
       <c r="I74" s="20" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J74" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="K74" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="L74" s="20" t="s">
         <v>243</v>
-      </c>
-      <c r="K74" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="L74" s="20" t="s">
-        <v>245</v>
       </c>
       <c r="M74" s="20" t="s">
         <v>132</v>
       </c>
       <c r="N74" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="O74" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="P74" s="20" t="s">
         <v>247</v>
-      </c>
-      <c r="O74" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="P74" s="20" t="s">
-        <v>249</v>
       </c>
       <c r="Q74" s="20" t="s">
         <v>140</v>
@@ -10170,13 +10170,13 @@
     </row>
     <row r="75" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="21" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C75" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E75" s="7" t="n">
         <v>0.6</v>
@@ -10222,11 +10222,11 @@
         <v>-0.05265</v>
       </c>
       <c r="Q75" s="28" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="R75" s="8"/>
       <c r="S75" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
@@ -10273,13 +10273,13 @@
     </row>
     <row r="76" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="21" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C76" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E76" s="7" t="n">
         <v>0.6</v>
@@ -10325,11 +10325,11 @@
         <v>-0.05265</v>
       </c>
       <c r="Q76" s="28" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="R76" s="8"/>
       <c r="S76" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
@@ -10376,13 +10376,13 @@
     </row>
     <row r="77" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C77" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E77" s="7" t="n">
         <v>0.6</v>
@@ -10428,11 +10428,11 @@
         <v>-0.05265</v>
       </c>
       <c r="Q77" s="28" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="R77" s="8"/>
       <c r="S77" s="10" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
@@ -10479,13 +10479,13 @@
     </row>
     <row r="78" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="21" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C78" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E78" s="7" t="n">
         <v>1.8</v>
@@ -10531,11 +10531,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q78" s="28" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="R78" s="8"/>
       <c r="S78" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
@@ -10582,13 +10582,13 @@
     </row>
     <row r="79" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="21" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C79" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>1.8</v>
@@ -10634,11 +10634,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q79" s="28" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R79" s="8"/>
       <c r="S79" s="10" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
@@ -10685,13 +10685,13 @@
     </row>
     <row r="80" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="21" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C80" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E80" s="7" t="n">
         <v>1.8</v>
@@ -10737,11 +10737,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q80" s="28" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="R80" s="8"/>
       <c r="S80" s="10" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
@@ -10788,13 +10788,13 @@
     </row>
     <row r="81" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="21" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>2.4</v>
@@ -10840,11 +10840,11 @@
         <v>-0.01755</v>
       </c>
       <c r="Q81" s="28" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R81" s="8"/>
       <c r="S81" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
@@ -10891,13 +10891,13 @@
     </row>
     <row r="82" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="21" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C82" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E82" s="7" t="n">
         <v>3</v>
@@ -10943,11 +10943,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q82" s="28" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="R82" s="8"/>
       <c r="S82" s="10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
@@ -10994,13 +10994,13 @@
     </row>
     <row r="83" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="21" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C83" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>3</v>
@@ -11046,11 +11046,11 @@
         <v>-0.05265</v>
       </c>
       <c r="Q83" s="28" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="R83" s="8"/>
       <c r="S83" s="10" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
@@ -11097,13 +11097,13 @@
     </row>
     <row r="84" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="21" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C84" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E84" s="7" t="n">
         <v>3</v>
@@ -11149,11 +11149,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q84" s="28" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="R84" s="8"/>
       <c r="S84" s="10" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
@@ -11200,13 +11200,13 @@
     </row>
     <row r="85" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C85" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>3</v>
@@ -11252,11 +11252,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q85" s="28" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="R85" s="8"/>
       <c r="S85" s="10" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="T85" s="1"/>
       <c r="U85" s="1"/>
@@ -11303,13 +11303,13 @@
     </row>
     <row r="86" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="21" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C86" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E86" s="7" t="n">
         <v>4.2</v>
@@ -11355,11 +11355,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q86" s="28" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="R86" s="8"/>
       <c r="S86" s="10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="T86" s="1"/>
       <c r="U86" s="1"/>
@@ -11406,13 +11406,13 @@
     </row>
     <row r="87" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="21" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C87" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>4.2</v>
@@ -11458,11 +11458,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q87" s="28" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="R87" s="8"/>
       <c r="S87" s="10" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
@@ -11509,13 +11509,13 @@
     </row>
     <row r="88" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="21" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C88" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E88" s="7" t="n">
         <v>5.4</v>
@@ -11561,11 +11561,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q88" s="28" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="R88" s="8"/>
       <c r="S88" s="10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
@@ -11612,13 +11612,13 @@
     </row>
     <row r="89" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="21" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C89" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>5.4</v>
@@ -11664,11 +11664,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q89" s="28" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="R89" s="8"/>
       <c r="S89" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
@@ -11715,13 +11715,13 @@
     </row>
     <row r="90" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="21" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C90" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E90" s="7" t="n">
         <v>6.6</v>
@@ -11767,11 +11767,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q90" s="8" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="R90" s="8"/>
       <c r="S90" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
@@ -11818,13 +11818,13 @@
     </row>
     <row r="91" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="21" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C91" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>6.6</v>
@@ -11870,11 +11870,11 @@
         <v>-0.0351</v>
       </c>
       <c r="Q91" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="R91" s="8"/>
       <c r="S91" s="10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
@@ -11921,13 +11921,13 @@
     </row>
     <row r="92" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="21" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C92" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E92" s="7" t="n">
         <v>6.6</v>
@@ -11973,11 +11973,11 @@
         <v>-0.0702</v>
       </c>
       <c r="Q92" s="8" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="R92" s="8"/>
       <c r="S92" s="10" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
@@ -12024,13 +12024,13 @@
     </row>
     <row r="93" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="21" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C93" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>7.8</v>
@@ -12076,11 +12076,11 @@
         <v>-0.0702000000000001</v>
       </c>
       <c r="Q93" s="8" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="R93" s="8"/>
       <c r="S93" s="10" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
@@ -12127,13 +12127,13 @@
     </row>
     <row r="94" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C94" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E94" s="23" t="n">
         <v>9</v>
@@ -12179,11 +12179,11 @@
         <v>-0.0482625</v>
       </c>
       <c r="Q94" s="8" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="R94" s="8"/>
       <c r="S94" s="10" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="T94" s="1"/>
       <c r="U94" s="1"/>
@@ -12230,13 +12230,13 @@
     </row>
     <row r="95" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="21" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C95" s="8" t="n">
         <v>9</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E95" s="23" t="n">
         <v>9.45</v>
@@ -12283,11 +12283,11 @@
         <v>-0.0418275</v>
       </c>
       <c r="Q95" s="8" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="R95" s="8"/>
       <c r="S95" s="10" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
@@ -12337,7 +12337,7 @@
         <v>141</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>143</v>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="R96" s="8"/>
       <c r="S96" s="10" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="T96" s="29"/>
       <c r="U96" s="29"/>
@@ -12440,10 +12440,10 @@
     </row>
     <row r="97" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B97" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C97" s="25" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D97" s="25"/>
       <c r="E97" s="25"/>
@@ -12462,10 +12462,10 @@
     </row>
     <row r="98" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D98" s="25"/>
       <c r="E98" s="25"/>
@@ -12489,7 +12489,7 @@
     </row>
     <row r="100" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -12553,7 +12553,7 @@
     </row>
     <row r="101" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
@@ -12617,10 +12617,10 @@
     </row>
     <row r="102" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="5" t="s">
@@ -12635,7 +12635,7 @@
       <c r="L102" s="5"/>
       <c r="M102" s="5"/>
       <c r="N102" s="5" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="O102" s="5" t="s">
         <v>122</v>
@@ -12644,7 +12644,7 @@
         <v>123</v>
       </c>
       <c r="Q102" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="R102" s="5"/>
       <c r="S102" s="5" t="s">
@@ -12695,14 +12695,14 @@
     </row>
     <row r="103" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="21" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="8" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
@@ -12730,7 +12730,7 @@
       </c>
       <c r="R103" s="8"/>
       <c r="S103" s="10" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="T103" s="1"/>
       <c r="U103" s="1"/>
@@ -12777,14 +12777,14 @@
     </row>
     <row r="104" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="21" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F104" s="8"/>
       <c r="G104" s="8"/>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="R104" s="8"/>
       <c r="S104" s="10" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
@@ -12859,10 +12859,10 @@
     </row>
     <row r="105" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B105" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D105" s="25"/>
       <c r="E105" s="25"/>
@@ -12939,7 +12939,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -12959,7 +12959,7 @@
     </row>
     <row r="2" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -12980,7 +12980,7 @@
     <row r="3" s="1" customFormat="true" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -13003,46 +13003,46 @@
         <v>114</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>491</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>493</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>122</v>
       </c>
       <c r="K5" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="O5" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="P5" s="5" t="s">
         <v>497</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>499</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>7</v>
@@ -13056,10 +13056,10 @@
       <c r="D6" s="20"/>
       <c r="E6" s="20"/>
       <c r="F6" s="20" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>130</v>
@@ -13068,29 +13068,29 @@
         <v>131</v>
       </c>
       <c r="J6" s="20" t="s">
+        <v>500</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>501</v>
+      </c>
+      <c r="M6" s="20" t="s">
         <v>502</v>
       </c>
-      <c r="K6" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="L6" s="20" t="s">
+      <c r="N6" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="O6" s="20" t="s">
         <v>503</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>504</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="O6" s="20" t="s">
-        <v>505</v>
       </c>
       <c r="P6" s="20"/>
       <c r="Q6" s="20"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>7</v>
@@ -13099,7 +13099,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F7" s="23" t="n">
         <v>0</v>
@@ -13141,15 +13141,15 @@
         <v>7 FX 486.86 FZ 486.86</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Q7" s="10" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="true" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>8</v>
@@ -13158,7 +13158,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F8" s="23" t="n">
         <f aca="false">DATOS!$C$30</f>
@@ -13201,15 +13201,15 @@
         <v>8 FX 486.86 FZ 486.86</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="true" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>75</v>
@@ -13218,7 +13218,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F9" s="23" t="n">
         <v>0</v>
@@ -13260,15 +13260,15 @@
         <v>75 FX 778.98 FZ 778.98</v>
       </c>
       <c r="P9" s="9" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="21" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>76</v>
@@ -13277,7 +13277,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F10" s="23" t="n">
         <f aca="false">DATOS!$C$30</f>
@@ -13320,15 +13320,15 @@
         <v>76 FX 778.98 FZ 778.98</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="21" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>9</v>
@@ -13337,7 +13337,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F11" s="23" t="n">
         <v>0</v>
@@ -13379,15 +13379,15 @@
         <v>9 FX 292.12 FZ 292.12</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>10</v>
@@ -13396,7 +13396,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F12" s="23" t="n">
         <f aca="false">DATOS!$C$30</f>
@@ -13439,18 +13439,18 @@
         <v>10 FX 292.12 FZ 292.12</v>
       </c>
       <c r="P12" s="9" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="true" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="25"/>
@@ -13524,7 +13524,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -13539,7 +13539,7 @@
     </row>
     <row r="2" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -13555,7 +13555,7 @@
     <row r="3" s="1" customFormat="true" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -13573,31 +13573,31 @@
         <v>114</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>520</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>522</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>122</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>7</v>
@@ -13617,25 +13617,25 @@
         <v>129</v>
       </c>
       <c r="H6" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>523</v>
+      </c>
+      <c r="J6" s="20" t="s">
         <v>524</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="K6" s="20" t="s">
         <v>525</v>
-      </c>
-      <c r="J6" s="20" t="s">
-        <v>526</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>527</v>
       </c>
       <c r="L6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>1</v>
@@ -13664,15 +13664,15 @@
         <v>52.65</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>1</v>
@@ -13701,15 +13701,15 @@
         <v>31.59</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>2</v>
@@ -13738,15 +13738,15 @@
         <v>70.2</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
@@ -13775,15 +13775,15 @@
         <v>42.12</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>3</v>
@@ -13812,15 +13812,15 @@
         <v>70.2</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>3</v>
@@ -13849,15 +13849,15 @@
         <v>42.12</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="21" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>4</v>
@@ -13886,15 +13886,15 @@
         <v>70.2</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>4</v>
@@ -13923,15 +13923,15 @@
         <v>42.12</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>5</v>
@@ -13960,15 +13960,15 @@
         <v>70.2</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>5</v>
@@ -13997,15 +13997,15 @@
         <v>42.12</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>6</v>
@@ -14034,15 +14034,15 @@
         <v>70.2</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
@@ -14071,15 +14071,15 @@
         <v>42.12</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>7</v>
@@ -14108,15 +14108,15 @@
         <v>70.2</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>7</v>
@@ -14145,15 +14145,15 @@
         <v>42.12</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>8</v>
@@ -14182,15 +14182,15 @@
         <v>48.2625</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="21" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>8</v>
@@ -14219,15 +14219,15 @@
         <v>34.321482</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="21" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>9</v>
@@ -14256,15 +14256,15 @@
         <v>34.2409275</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="true" ht="20.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="21" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>10</v>
@@ -14293,15 +14293,15 @@
         <v>21.0784275</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="true" ht="20.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="21" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>10</v>
@@ -14330,15 +14330,15 @@
         <v>13.261482</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>1</v>
@@ -14367,15 +14367,15 @@
         <v>52.65</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>1</v>
@@ -14404,15 +14404,15 @@
         <v>31.59</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>2</v>
@@ -14441,15 +14441,15 @@
         <v>70.2</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>2</v>
@@ -14478,15 +14478,15 @@
         <v>42.12</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>3</v>
@@ -14515,15 +14515,15 @@
         <v>70.2</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>3</v>
@@ -14552,15 +14552,15 @@
         <v>42.12</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>4</v>
@@ -14589,15 +14589,15 @@
         <v>70.2</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>4</v>
@@ -14626,15 +14626,15 @@
         <v>42.12</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>5</v>
@@ -14663,15 +14663,15 @@
         <v>70.2</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>5</v>
@@ -14700,15 +14700,15 @@
         <v>42.12</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="21" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>6</v>
@@ -14737,15 +14737,15 @@
         <v>70.2</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="21" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>6</v>
@@ -14774,15 +14774,15 @@
         <v>42.12</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="21" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>7</v>
@@ -14811,15 +14811,15 @@
         <v>70.2</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="21" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>7</v>
@@ -14848,15 +14848,15 @@
         <v>42.12</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="21" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>8</v>
@@ -14885,15 +14885,15 @@
         <v>48.2625</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="21" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>8</v>
@@ -14922,15 +14922,15 @@
         <v>34.321482</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>9</v>
@@ -14959,15 +14959,15 @@
         <v>34.2409275</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="21" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>10</v>
@@ -14996,15 +14996,15 @@
         <v>21.0784275</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="21" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>10</v>
@@ -15033,7 +15033,7 @@
         <v>13.261482</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
@@ -15087,10 +15087,10 @@
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D45" s="25"/>
       <c r="E45" s="25"/>
@@ -15146,7 +15146,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -15155,7 +15155,7 @@
     </row>
     <row r="2" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -15165,7 +15165,7 @@
     <row r="3" s="1" customFormat="true" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -15177,16 +15177,16 @@
         <v>114</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15197,10 +15197,10 @@
         <v>41</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F6" s="21" t="str">
         <f aca="false">IF(LEN($D6)&gt;79,"MÁS DE 79","")</f>
@@ -15209,10 +15209,10 @@
     </row>
     <row r="7" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D7" s="6" t="str">
         <f aca="false">"74 121 TO 124 285 TO 287 310 TO 326 352 TO 371 UNI GY "&amp;TEXT(-TECHO!K9/100,"0.0000")</f>
@@ -15232,7 +15232,7 @@
         <v>146</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D8" s="6" t="str">
         <f aca="false">"327 372 TO 375 UNI GY "&amp;TEXT(-TECHO!K8/100,"0.0000")</f>
@@ -15252,7 +15252,7 @@
         <v>141</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D9" s="6" t="str">
         <f aca="false">"11 48 TO 51 UNI GY "&amp;TEXT(-TECHO!K7/100,"0.0000")</f>
@@ -15269,10 +15269,10 @@
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D10" s="6" t="str">
         <f aca="false">"12 52 TO 55 UNI GY "&amp;TEXT(-TECHO!K18/100,"0.0000")</f>
@@ -15289,17 +15289,17 @@
     </row>
     <row r="11" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="21" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D11" s="6" t="str">
         <f aca="false">"20 21 24 25 28 29 32 33 36 37 40 41 507 TO 542 UNI GY "&amp;TEXT(MUROS!Q9,"0.0000")</f>
         <v>20 21 24 25 28 29 32 33 36 37 40 41 507 TO 542 UNI GY -0.0702</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F11" s="21" t="str">
         <f aca="false">IF(LEN($D11)&gt;79,"MÁS DE 79","")</f>
@@ -15308,17 +15308,17 @@
     </row>
     <row r="12" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D12" s="6" t="str">
         <f aca="false">"201 202 205 TO 214 553 TO 576 UNI GY "&amp;TEXT(MUROS!Q10,"0.0000")</f>
         <v>201 202 205 TO 214 553 TO 576 UNI GY -0.0702</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F12" s="21" t="str">
         <f aca="false">IF(LEN($D12)&gt;79,"MÁS DE 79","")</f>
@@ -15327,17 +15327,17 @@
     </row>
     <row r="13" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="21" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D13" s="6" t="str">
         <f aca="false">"23 27 31 68 153 155 161 203 233 793 794 824 UNI GY "&amp;TEXT(MUROS!P78,"0.0000")</f>
         <v>23 27 31 68 153 155 161 203 233 793 794 824 UNI GY -0.0702</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F13" s="21" t="str">
         <f aca="false">IF(LEN($D13)&gt;79,"MÁS DE 79","")</f>
@@ -15346,17 +15346,17 @@
     </row>
     <row r="14" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="21" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D14" s="6" t="str">
         <f aca="false">"16 17 46 149 159 199 200 501 TO 506 549 TO 552 823 UNI GY "&amp;TEXT(MUROS!Q7,"0.0000")</f>
         <v>16 17 46 149 159 199 200 501 TO 506 549 TO 552 823 UNI GY -0.0527</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F14" s="21" t="str">
         <f aca="false">IF(LEN($D14)&gt;79,"MÁS DE 79","")</f>
@@ -15365,17 +15365,17 @@
     </row>
     <row r="15" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="21" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D15" s="6" t="str">
         <f aca="false">"44 45 543 TO 548 UNI GY "&amp;TEXT(MUROS!Q21,"0.0000")</f>
         <v>44 45 543 TO 548 UNI GY -0.0483</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F15" s="21" t="str">
         <f aca="false">IF(LEN($D15)&gt;79,"MÁS DE 79","")</f>
@@ -15384,17 +15384,17 @@
     </row>
     <row r="16" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="21" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D16" s="6" t="str">
         <f aca="false">"215 216 577 TO 580 UNI GY "&amp;TEXT(MUROS!Q22,"0.0000")</f>
         <v>215 216 577 TO 580 UNI GY -0.0572</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F16" s="21" t="str">
         <f aca="false">IF(LEN($D16)&gt;79,"MÁS DE 79","")</f>
@@ -15403,17 +15403,17 @@
     </row>
     <row r="17" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="21" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D17" s="6" t="str">
         <f aca="false">"843 844 867 TO 872 UNI GY "&amp;TEXT(MUROS!Q23,"0.0000")</f>
         <v>843 844 867 TO 872 UNI GY -0.0342</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F17" s="21" t="str">
         <f aca="false">IF(LEN($D17)&gt;79,"MÁS DE 79","")</f>
@@ -15477,17 +15477,17 @@
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D18" s="6" t="str">
         <f aca="false">"204 UNI GY "&amp;TEXT(MUROS!P81,"0.0000")</f>
         <v>204 UNI GY -0.0176</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F18" s="21" t="str">
         <f aca="false">IF(LEN($D18)&gt;79,"MÁS DE 79","")</f>
@@ -15496,17 +15496,17 @@
     </row>
     <row r="19" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D19" s="6" t="str">
         <f aca="false">"35 157 UNI GY "&amp;TEXT(MUROS!P88,"0.0000")</f>
         <v>35 157 UNI GY -0.0702</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F19" s="21" t="str">
         <f aca="false">IF(LEN($D19)&gt;79,"MÁS DE 79","")</f>
@@ -15515,17 +15515,17 @@
     </row>
     <row r="20" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="21" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D20" s="6" t="str">
         <f aca="false">"234 807 808 UNI GY "&amp;TEXT(MUROS!P91,"0.0000")</f>
         <v>234 807 808 UNI GY -0.0351</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F20" s="21" t="str">
         <f aca="false">IF(LEN($D20)&gt;79,"MÁS DE 79","")</f>
@@ -15534,17 +15534,17 @@
     </row>
     <row r="21" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D21" s="6" t="str">
         <f aca="false">"39 581 TO 584 UNI GY "&amp;TEXT(MUROS!P93,"0.0000")</f>
         <v>39 581 TO 584 UNI GY -0.0702</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F21" s="21" t="str">
         <f aca="false">IF(LEN($D21)&gt;79,"MÁS DE 79","")</f>
@@ -15553,17 +15553,17 @@
     </row>
     <row r="22" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D22" s="6" t="str">
         <f aca="false">"43 585 TO 588 UNI GY "&amp;TEXT(MUROS!P94,"0.0000")</f>
         <v>43 585 TO 588 UNI GY -0.0483</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F22" s="21" t="str">
         <f aca="false">IF(LEN($D22)&gt;79,"MÁS DE 79","")</f>
@@ -15572,17 +15572,17 @@
     </row>
     <row r="23" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="21" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D23" s="6" t="str">
         <f aca="false">"840 863 TO 866 UNI GY "&amp;TEXT(MUROS!P95,"0.0000")</f>
         <v>840 863 TO 866 UNI GY -0.0418</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F23" s="21" t="str">
         <f aca="false">IF(LEN($D23)&gt;79,"MÁS DE 79","")</f>
@@ -15591,17 +15591,17 @@
     </row>
     <row r="24" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="21" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D24" s="6" t="str">
         <f aca="false">"11 48 TO 51 UNI GY "&amp;TEXT(MUROS!P96,"0.0000")</f>
         <v>11 48 TO 51 UNI GY -0.0287</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F24" s="21" t="str">
         <f aca="false">IF(LEN($D24)&gt;79,"MÁS DE 79","")</f>
@@ -15610,17 +15610,17 @@
     </row>
     <row r="25" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="21" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D25" s="6" t="str">
         <f aca="false">"241 242 269 TO 280 UNI GY "&amp;TEXT(MUROS!Q103,"0.0000")</f>
         <v>241 242 269 TO 280 UNI GY -0.0211</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F25" s="21" t="str">
         <f aca="false">IF(LEN($D25)&gt;79,"MÁS DE 79","")</f>
@@ -15629,17 +15629,17 @@
     </row>
     <row r="26" s="1" customFormat="true" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D26" s="6" t="str">
         <f aca="false">"243 TO 250 UNI GY "&amp;TEXT(MUROS!Q104,"0.0000")</f>
         <v>243 TO 250 UNI GY -0.0221</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F26" s="21" t="str">
         <f aca="false">IF(LEN($D26)&gt;79,"MÁS DE 79","")</f>
@@ -15654,10 +15654,10 @@
         <v>41</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F27" s="21" t="str">
         <f aca="false">IF(LEN($D27)&gt;79,"MÁS DE 79","")</f>
@@ -15666,17 +15666,17 @@
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D28" s="6" t="str">
         <f aca="false">DATOS!$C$54&amp;" FY "&amp;TEXT(-DATOS!$C$53,"0.0")</f>
         <v>69 70 FY -198.9</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F28" s="21" t="str">
         <f aca="false">IF(LEN($D28)&gt;79,"MÁS DE 79","")</f>
@@ -15685,7 +15685,7 @@
     </row>
     <row r="29" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -15697,16 +15697,16 @@
         <v>114</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15717,10 +15717,10 @@
         <v>41</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F31" s="21" t="str">
         <f aca="false">IF(LEN($D31)&gt;79,"MÁS DE 79","")</f>
@@ -15729,10 +15729,10 @@
     </row>
     <row r="32" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="21" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D32" s="6" t="str">
         <f aca="false">"74 121 TO 124 285 TO 287 310 TO 326 352 TO 371 UNI GY "&amp;TEXT(-TECHO!L9/100,"0.0000")</f>
@@ -15752,7 +15752,7 @@
         <v>146</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D33" s="6" t="str">
         <f aca="false">"327 372 TO 375 UNI GY "&amp;TEXT(-TECHO!L8/100,"0.0000")</f>
@@ -15772,7 +15772,7 @@
         <v>141</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D34" s="6" t="str">
         <f aca="false">"11 48 TO 51 UNI GY "&amp;TEXT(-TECHO!L7/100,"0.0000")</f>
@@ -15789,10 +15789,10 @@
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D35" s="6" t="str">
         <f aca="false">"12 52 TO 55 UNI GY "&amp;TEXT(-TECHO!L18/100,"0.0000")</f>
@@ -15809,7 +15809,7 @@
     </row>
     <row r="37" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -15821,16 +15821,16 @@
         <v>114</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15838,14 +15838,14 @@
         <v>41</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D39" s="6" t="str">
         <f aca="false">IF(DATOS!$C$23=0,"* w_i = 0: el caso queda sin carga","Aplicar w_i × b como en el caso 2 (w_i = "&amp;DATOS!$C$23&amp;" kg/m²)")</f>
         <v>* w_i = 0: el caso queda sin carga</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F39" s="21" t="str">
         <f aca="false">IF(LEN($D39)&gt;79,"MÁS DE 79","")</f>
@@ -15854,7 +15854,7 @@
     </row>
     <row r="41" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -15866,13 +15866,13 @@
         <v>114</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F42" s="5"/>
     </row>
@@ -15884,7 +15884,7 @@
         <v>83</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E43" s="9"/>
       <c r="F43" s="21" t="str">
@@ -15894,16 +15894,16 @@
     </row>
     <row r="44" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="21" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>83</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F44" s="21" t="str">
         <f aca="false">IF(LEN($D44)&gt;79,"MÁS DE 79","")</f>
@@ -15912,16 +15912,16 @@
     </row>
     <row r="45" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="21" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>83</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F45" s="21" t="str">
         <f aca="false">IF(LEN($D45)&gt;79,"MÁS DE 79","")</f>
@@ -15930,16 +15930,16 @@
     </row>
     <row r="46" s="1" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="21" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>83</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F46" s="21" t="str">
         <f aca="false">IF(LEN($D46)&gt;79,"MÁS DE 79","")</f>
@@ -15948,16 +15948,16 @@
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="21" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>83</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F47" s="21" t="str">
         <f aca="false">IF(LEN($D47)&gt;79,"MÁS DE 79","")</f>
@@ -15972,10 +15972,10 @@
         <v>83</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F48" s="21" t="str">
         <f aca="false">IF(LEN($D48)&gt;79,"MÁS DE 79","")</f>
@@ -15990,10 +15990,10 @@
         <v>83</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F49" s="21" t="str">
         <f aca="false">IF(LEN($D49)&gt;79,"MÁS DE 79","")</f>
@@ -16009,7 +16009,7 @@
     </row>
     <row r="51" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="21" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="6"/>
@@ -16172,7 +16172,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:BI73"/>
+  <dimension ref="B1:BI71"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.77"/>
@@ -16185,7 +16185,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -16194,7 +16194,7 @@
     </row>
     <row r="2" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -16204,7 +16204,7 @@
     <row r="3" s="1" customFormat="true" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -16230,89 +16230,89 @@
     </row>
     <row r="6" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C6" s="11" t="n">
         <f aca="false">TECHO!$J$19</f>
         <v>161.28</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>638</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">MUROS!$O$41</f>
         <v>299.14014</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">MUROS!$O$69</f>
         <v>11.74014</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">MUROS!$N$97</f>
         <v>67.4184</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">C7+C8+C9</f>
         <v>378.29868</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>41</v>
@@ -16320,7 +16320,7 @@
     </row>
     <row r="12" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -16346,7 +16346,7 @@
     </row>
     <row r="14" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">DATOS!$C$8*C6</f>
@@ -16356,15 +16356,15 @@
         <v>58</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C15" s="19" t="n">
         <f aca="false">DATOS!$C$10*C10</f>
@@ -16374,15 +16374,15 @@
         <v>58</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">DATOS!$C$22*C6</f>
@@ -16392,15 +16392,15 @@
         <v>58</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">DATOS!$C$23*C6</f>
@@ -16410,15 +16410,15 @@
         <v>58</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">DATOS!$C$52</f>
@@ -16428,20 +16428,20 @@
         <v>58</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="31" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="32" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16449,21 +16449,21 @@
         <v>116</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>668</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>669</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>19.8225</v>
@@ -16475,12 +16475,12 @@
         <v>1061.899</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>20.86</v>
@@ -16492,12 +16492,12 @@
         <v>684.191</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>19.2</v>
@@ -16509,7 +16509,7 @@
         <v>343.498</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16517,203 +16517,203 @@
         <v>143</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>10.08</v>
+        <v>30.24</v>
       </c>
       <c r="D26" s="33" t="n">
-        <v>7.8846</v>
+        <v>16.5577</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>62.257</v>
+        <v>392.223</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>142</v>
+        <v>675</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>10.08</v>
+        <v>32.043</v>
       </c>
       <c r="D27" s="33" t="n">
-        <v>16.5577</v>
+        <v>18.4851</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>130.741</v>
+        <v>463.987</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>167</v>
+        <v>676</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>10.08</v>
+        <v>90.72</v>
       </c>
       <c r="D28" s="33" t="n">
-        <v>10.7756</v>
+        <v>9.2425</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>85.085</v>
+        <v>656.818</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>208</v>
+        <v>456</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>32.043</v>
+        <v>150.08</v>
       </c>
       <c r="D29" s="33" t="n">
-        <v>18.4851</v>
+        <v>11.5552</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>463.987</v>
+        <v>1358.473</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>148</v>
+        <v>460</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>90.72</v>
+        <v>114.08</v>
       </c>
       <c r="D30" s="33" t="n">
-        <v>9.2425</v>
+        <v>8.2789</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>656.818</v>
+        <v>739.831</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>150.08</v>
+        <v>52.16</v>
       </c>
       <c r="D31" s="33" t="n">
-        <v>11.5552</v>
+        <v>16.5577</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>1358.473</v>
+        <v>676.532</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>462</v>
+        <v>399</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>114.08</v>
+        <v>23.68</v>
       </c>
       <c r="D32" s="33" t="n">
-        <v>8.2789</v>
+        <v>3.9423</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>739.831</v>
+        <v>73.128</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>448</v>
+        <v>682</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>52.16</v>
+        <v>6</v>
       </c>
       <c r="D33" s="33" t="n">
-        <v>16.5577</v>
+        <v>5.4193</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>676.532</v>
+        <v>25.471</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>401</v>
+        <v>684</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>23.68</v>
+        <v>13.2</v>
       </c>
       <c r="D34" s="33" t="n">
-        <v>3.9423</v>
+        <v>17.4193</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>73.128</v>
+        <v>180.118</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>6</v>
+        <v>64.0861</v>
       </c>
       <c r="D35" s="33" t="n">
-        <v>5.4193</v>
+        <v>2.0129</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>25.471</v>
+        <v>101.05</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>13.2</v>
+        <v>104.1</v>
       </c>
       <c r="D36" s="33" t="n">
-        <v>17.4193</v>
+        <v>1.5097</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>180.118</v>
+        <v>123.108</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>64.0861</v>
+        <v>147.3309</v>
       </c>
       <c r="D37" s="33" t="n">
-        <v>2.0129</v>
+        <v>1.2668</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>101.05</v>
+        <v>146.198</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="G37" s="0"/>
       <c r="H37" s="0"/>
@@ -16773,370 +16773,372 @@
     </row>
     <row r="38" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>104.1</v>
+        <v>21.5662</v>
       </c>
       <c r="D38" s="33" t="n">
-        <v>1.5097</v>
+        <v>1.9793</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>123.108</v>
+        <v>33.438</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>691</v>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>147.3309</v>
-      </c>
-      <c r="D39" s="33" t="n">
-        <v>1.2668</v>
-      </c>
+        <v>694</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <f aca="false">SUM(C23:C38)</f>
+        <v>909.1687</v>
+      </c>
+      <c r="D39" s="8"/>
       <c r="E39" s="19" t="n">
-        <v>146.198</v>
+        <f aca="false">SUM(E23:E38)</f>
+        <v>7059.963</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="6" t="s">
-        <v>693</v>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>21.5662</v>
-      </c>
-      <c r="D40" s="33" t="n">
-        <v>1.9793</v>
-      </c>
-      <c r="E40" s="19" t="n">
-        <v>33.438</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>694</v>
-      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="10"/>
     </row>
     <row r="41" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="6" t="s">
-        <v>695</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <f aca="false">SUM(C23:C40)</f>
-        <v>909.1687</v>
-      </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="19" t="n">
-        <f aca="false">SUM(E23:E40)</f>
-        <v>6945.823</v>
-      </c>
-      <c r="F41" s="10" t="s">
+      <c r="B41" s="31" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="6"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="10"/>
-    </row>
-    <row r="43" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="31" t="s">
+      <c r="B42" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="6" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="44" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="6" t="s">
+      <c r="C43" s="11" t="n">
+        <f aca="false">E39/1000</f>
+        <v>7.059963</v>
+      </c>
+      <c r="D43" s="8" t="s">
         <v>698</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <f aca="false">E41/1000</f>
-        <v>6.945823</v>
-      </c>
-      <c r="D45" s="8" t="s">
+      <c r="E43" s="9" t="s">
         <v>699</v>
       </c>
-      <c r="E45" s="9" t="s">
-        <v>700</v>
-      </c>
-      <c r="F45" s="10" t="s">
+      <c r="F43" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="6" t="s">
+    <row r="44" s="1" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="11" t="n">
+      <c r="C44" s="11" t="n">
         <f aca="false">C14/1000</f>
         <v>3.1159296</v>
       </c>
-      <c r="D46" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="E46" s="9" t="s">
+      <c r="D44" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>701</v>
       </c>
-      <c r="F46" s="10" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="6" t="s">
+    </row>
+    <row r="45" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C47" s="11" t="n">
+      <c r="C45" s="11" t="n">
         <f aca="false">C15/1000</f>
         <v>2.213047278</v>
       </c>
+      <c r="D45" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <f aca="false">C18/1000</f>
+        <v>0.3978</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <f aca="false">C17/1000</f>
+        <v>0</v>
+      </c>
       <c r="D47" s="8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>643</v>
+        <v>708</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="6" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C48" s="11" t="n">
-        <f aca="false">C18/1000</f>
-        <v>0.3978</v>
+        <f aca="false">SUM(C43:C47)</f>
+        <v>12.786739878</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="6" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C49" s="11" t="n">
-        <f aca="false">C17/1000</f>
-        <v>0</v>
+        <v>12.80125</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="6" t="s">
-        <v>710</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <f aca="false">SUM(C45:C49)</f>
-        <v>12.672599878</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>711</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>712</v>
-      </c>
+        <v>714</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="6"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="6" t="s">
-        <v>713</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>12.62174</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="F51" s="10" t="s">
+      <c r="B51" s="31" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="6"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="10"/>
+      <c r="B52" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="6" t="s">
         <v>716</v>
       </c>
+      <c r="C53" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>718</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>7</v>
+      <c r="B54" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="6" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>41</v>
       </c>
       <c r="E55" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="F55" s="10" t="s">
         <v>718</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="6" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>41</v>
+        <v>722</v>
       </c>
       <c r="E56" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="F56" s="10" t="s">
         <v>718</v>
-      </c>
-      <c r="F56" s="10" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>41</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="6" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>0.6</v>
+        <v>0.085</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>723</v>
+        <v>41</v>
       </c>
       <c r="E58" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="F58" s="10" t="s">
         <v>718</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="6" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>7</v>
+        <f aca="false">DATOS!$C$15</f>
+        <v>10.43</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>726</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="6" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>0.085</v>
+        <f aca="false">C58*C59^0.75</f>
+        <v>0.493323900968996</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>41</v>
+        <v>722</v>
       </c>
       <c r="E60" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="F60" s="10" t="s">
         <v>718</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="6" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C61" s="11" t="n">
-        <f aca="false">DATOS!$C$15</f>
-        <v>10.43</v>
+        <f aca="false">C53*C54*C55/C57*(C56/MAX(C60,C56))^(2/3)</f>
+        <v>0.171428571428571</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>83</v>
@@ -17144,209 +17146,173 @@
     </row>
     <row r="62" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="6" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C62" s="11" t="n">
-        <f aca="false">C60*C61^0.75</f>
-        <v>0.493323900968996</v>
+        <v>0.7201</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>719</v>
+        <v>735</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="6" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C63" s="11" t="n">
-        <f aca="false">C55*C56*C57/C59*(C58/MAX(C62,C58))^(2/3)</f>
-        <v>0.171428571428571</v>
+        <v>0.36825</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>41</v>
+        <v>722</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>83</v>
+        <v>735</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="6" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>0.72307</v>
+        <v>1943.33686</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>723</v>
+        <v>58</v>
       </c>
       <c r="E64" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="F64" s="10" t="s">
         <v>735</v>
       </c>
-      <c r="F64" s="10" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="6" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>0.3699</v>
+        <v>2194.5</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>723</v>
+        <v>58</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="6" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>1916.08574</v>
+        <v>1755.6</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="6" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2163.72686</v>
+        <v>1975.05</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="6" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>1730.98149</v>
+        <v>1621.54716</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="6" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>1947.35417</v>
+        <v>1959.37441</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="6" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>1579.06</v>
+        <f aca="false">MAX(1,C66/C68)</f>
+        <v>1.08266971402793</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>736</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="6" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>1845.9</v>
+        <f aca="false">MAX(1,C67/C69)</f>
+        <v>1.00800030352545</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="6" t="s">
-        <v>748</v>
-      </c>
-      <c r="C72" s="11" t="n">
-        <f aca="false">MAX(1,C68/C70)</f>
-        <v>1.09621008068091</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>749</v>
-      </c>
-      <c r="F72" s="10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="6" t="s">
-        <v>750</v>
-      </c>
-      <c r="C73" s="11" t="n">
-        <f aca="false">MAX(1,C69/C71)</f>
-        <v>1.05496189934449</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="F73" s="10" t="s">
         <v>83</v>
       </c>
     </row>
